--- a/Data Sets/MySQL - Joins/join.xlsx
+++ b/Data Sets/MySQL - Joins/join.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Projects\MySQL - Joins\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Data Sets\MySQL - Joins\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F22BAB-CBB0-4D03-B052-45AD74798329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E939331-7604-4A25-9EE2-47793F3F3402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
